--- a/Gravedigger2026/Assets/ConfigTables/Excel/战斗_技能配置表_Combat_SkillConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Excel/战斗_技能配置表_Combat_SkillConfig.xlsx
@@ -1,52 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr codeName="ThisWorkbook"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -65,13 +47,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -150,7 +199,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -185,7 +233,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -220,16 +267,20 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -351,178 +402,242 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:spDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </a:style>
-    </a:spDef>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C11"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
-        <v>SkillId</v>
-      </c>
-      <c r="B1" t="str">
-        <v>BaseCooldownSeconds</v>
-      </c>
-      <c r="C1" t="str">
-        <v>LossOfControlChanceBonus</v>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>技能ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>基础冷却</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>失控概率加成</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v>Skill_01</v>
-      </c>
-      <c r="B2">
-        <v>5</v>
-      </c>
-      <c r="C2">
-        <v>0.02</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>主键；被灵魂/宝石/装备/怪物 Skills 引用</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>≥0 秒；实际 CD 见 §3.12 公式</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>可正可负；缺省 0</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v>Skill_02</v>
-      </c>
-      <c r="B3">
-        <v>6</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>SkillId</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>BaseCooldownSeconds</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>LossOfControlChanceBonus</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
-        <v>Skill_03</v>
-      </c>
-      <c r="B4">
-        <v>7</v>
-      </c>
-      <c r="C4">
-        <v>-0.01</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Skill_01</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="str">
-        <v>Skill_04</v>
-      </c>
-      <c r="B5">
-        <v>8</v>
-      </c>
-      <c r="C5">
-        <v>0.02</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Skill_02</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="str">
-        <v>Skill_05</v>
-      </c>
-      <c r="B6">
-        <v>9</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Skill_03</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>-0.01</t>
+        </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="str">
-        <v>Skill_06</v>
-      </c>
-      <c r="B7">
-        <v>10</v>
-      </c>
-      <c r="C7">
-        <v>-0.01</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Skill_04</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="str">
-        <v>Skill_07</v>
-      </c>
-      <c r="B8">
-        <v>11</v>
-      </c>
-      <c r="C8">
-        <v>0.02</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Skill_05</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="str">
-        <v>Skill_08</v>
-      </c>
-      <c r="B9">
-        <v>12</v>
-      </c>
-      <c r="C9">
-        <v>0</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Skill_06</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>-0.01</t>
+        </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="str">
-        <v>Skill_09</v>
-      </c>
-      <c r="B10">
-        <v>13</v>
-      </c>
-      <c r="C10">
-        <v>-0.01</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Skill_07</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="str">
-        <v>Skill_10</v>
-      </c>
-      <c r="B11">
-        <v>14</v>
-      </c>
-      <c r="C11">
-        <v>0.02</v>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Skill_08</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Skill_09</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Skill_10</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C11"/>
-  </ignoredErrors>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Gravedigger2026/Assets/ConfigTables/Excel/战斗_技能配置表_Combat_SkillConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Excel/战斗_技能配置表_Combat_SkillConfig.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,10 +424,45 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>技能等级</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>技能CD模式</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>技能释放目标</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>额外激活条件</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>技能名称</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>技能展示描述</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>技能效果ID</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>基础冷却</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>失控概率加成</t>
         </is>
@@ -436,17 +471,52 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>主键；被灵魂/宝石/装备/怪物 Skills 引用</t>
+          <t>复合主键之一；被灵魂/宝石/装备 Skills 引用</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>复合主键之一；≥1；与 Skills 段内 Level 对齐</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Mode1=开战起算CD；Mode2=开战CD=0，释放后再进CD</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Self|AllySingle|AllyAll|EnemySingle|EnemyAll|GroundPoint|CurrentNormalAttackTarget</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>默认空；编码后续专题</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>展示文字或本地化 Key</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>展示文字或本地化 Key</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>FK → SkillEffectConfig.SkillEffectId</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>≥0 秒；实际 CD 见 §3.12 公式</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>可正可负；缺省 0</t>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>可正可负；缺省 0；按等级查行后求和</t>
         </is>
       </c>
     </row>
@@ -458,10 +528,45 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>SkillLevel</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CooldownMode</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>CastTarget</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>ExtraActivationCondition</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>DisplayName</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>SkillEffectId</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>BaseCooldownSeconds</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>LossOfControlChanceBonus</t>
         </is>
@@ -475,10 +580,41 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Mode1</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>CurrentNormalAttackTarget</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>技能01</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>技能01展示描述</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>SkillEffect_01</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>0.02</t>
         </is>
@@ -492,10 +628,41 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Mode1</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>CurrentNormalAttackTarget</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>技能02</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>技能02展示描述</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>SkillEffect_02</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -509,10 +676,41 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Mode2</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>CurrentNormalAttackTarget</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>技能03</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>技能03展示描述</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>SkillEffect_03</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>-0.01</t>
         </is>
@@ -526,10 +724,41 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Mode1</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>CurrentNormalAttackTarget</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>技能04</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>技能04展示描述</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>SkillEffect_04</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>0.02</t>
         </is>
@@ -543,10 +772,41 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Mode1</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>EnemySingle</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>技能05</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>技能05展示描述</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>SkillEffect_05</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -560,10 +820,41 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Mode2</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>技能06</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>技能06展示描述</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>SkillEffect_06</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>-0.01</t>
         </is>
@@ -577,10 +868,41 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Mode1</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>CurrentNormalAttackTarget</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>技能07</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>技能07展示描述</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>SkillEffect_07</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>0.02</t>
         </is>
@@ -594,10 +916,41 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Mode1</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>AllySingle</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>技能08</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>技能08展示描述</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>SkillEffect_08</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -611,10 +964,41 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Mode2</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>GroundPoint</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>技能09</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>技能09展示描述</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>SkillEffect_09</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>-0.01</t>
         </is>
@@ -628,10 +1012,41 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Mode1</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>EnemyAll</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>技能10</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>技能10展示描述</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>SkillEffect_10</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>0.02</t>
         </is>

--- a/Gravedigger2026/Assets/ConfigTables/Excel/战斗_技能配置表_Combat_SkillConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Excel/战斗_技能配置表_Combat_SkillConfig.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,15 +454,20 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>技能图标</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>技能效果ID</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>基础冷却</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>失控概率加成</t>
         </is>
@@ -506,15 +511,20 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
+          <t>UI 图标资源 Id；缺/空=无图</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>FK → SkillEffectConfig.SkillEffectId</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>≥0 秒；实际 CD 见 §3.12 公式</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>可正可负；缺省 0；按等级查行后求和</t>
         </is>
@@ -558,15 +568,20 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>IconAssetId</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>SkillEffectId</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>BaseCooldownSeconds</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>LossOfControlChanceBonus</t>
         </is>
@@ -593,7 +608,6 @@
           <t>CurrentNormalAttackTarget</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>技能01</t>
@@ -604,17 +618,17 @@
           <t>技能01展示描述</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>SkillEffect_01</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>0.02</t>
         </is>
@@ -623,13 +637,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Skill_02</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t>Skill_01</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -641,37 +653,35 @@
           <t>CurrentNormalAttackTarget</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>技能02</t>
+          <t>技能01</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>技能02展示描述</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>SkillEffect_02</t>
-        </is>
-      </c>
+          <t>技能01展示描述</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>SkillEffect_01</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>0.03</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Skill_03</t>
+          <t>Skill_02</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -681,7 +691,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Mode2</t>
+          <t>Mode1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -689,37 +699,36 @@
           <t>CurrentNormalAttackTarget</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>技能03</t>
+          <t>技能02</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>技能03展示描述</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>SkillEffect_03</t>
+          <t>技能02展示描述</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>SkillEffect_02</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Skill_04</t>
+          <t>Skill_03</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -729,7 +738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Mode1</t>
+          <t>Mode2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -737,37 +746,36 @@
           <t>CurrentNormalAttackTarget</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>技能04</t>
+          <t>技能03</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>技能04展示描述</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>SkillEffect_04</t>
+          <t>技能03展示描述</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>SkillEffect_03</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>-0.01</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Skill_05</t>
+          <t>Skill_04</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -782,40 +790,39 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>EnemySingle</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
+          <t>CurrentNormalAttackTarget</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>技能05</t>
+          <t>技能04</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>技能05展示描述</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>SkillEffect_05</t>
+          <t>技能04展示描述</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>SkillEffect_04</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0.02</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Skill_06</t>
+          <t>Skill_05</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -825,45 +832,44 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Mode2</t>
+          <t>Mode1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Self</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
+          <t>EnemySingle</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>技能06</t>
+          <t>技能05</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>技能06展示描述</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>SkillEffect_06</t>
+          <t>技能05展示描述</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>SkillEffect_05</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Skill_07</t>
+          <t>Skill_06</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -873,45 +879,44 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Mode1</t>
+          <t>Mode2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CurrentNormalAttackTarget</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
+          <t>Self</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>技能07</t>
+          <t>技能06</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>技能07展示描述</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>SkillEffect_07</t>
+          <t>技能06展示描述</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>SkillEffect_06</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>-0.01</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Skill_08</t>
+          <t>Skill_07</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -926,40 +931,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>AllySingle</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
+          <t>CurrentNormalAttackTarget</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>技能08</t>
+          <t>技能07</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>技能08展示描述</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>SkillEffect_08</t>
+          <t>技能07展示描述</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>SkillEffect_07</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0.02</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Skill_09</t>
+          <t>Skill_08</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -969,84 +973,129 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Mode2</t>
+          <t>Mode1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>GroundPoint</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
+          <t>AllySingle</t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>技能09</t>
+          <t>技能08</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>技能09展示描述</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>SkillEffect_09</t>
+          <t>技能08展示描述</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>SkillEffect_08</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>Skill_09</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Mode2</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>GroundPoint</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>技能09</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>技能09展示描述</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>SkillEffect_09</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>Skill_10</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Mode1</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>EnemyAll</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>技能10</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>技能10展示描述</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>SkillEffect_10</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>0.02</t>
         </is>

--- a/Gravedigger2026/Assets/ConfigTables/Excel/战斗_技能配置表_Combat_SkillConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Excel/战斗_技能配置表_Combat_SkillConfig.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,6 +472,11 @@
           <t>失控概率加成</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>效果已实现</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -529,6 +534,11 @@
           <t>可正可负；缺省 0；按等级查行后求和</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Demo 战斗效果是否已接线；不驱动战斗；UI-021 绿/红</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -586,6 +596,11 @@
           <t>LossOfControlChanceBonus</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>EffectImplemented</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -633,6 +648,9 @@
           <t>0.02</t>
         </is>
       </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -663,7 +681,6 @@
           <t>技能01展示描述</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>SkillEffect_01</t>
@@ -677,6 +694,9 @@
       <c r="K5" t="n">
         <v>0.03</v>
       </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -724,6 +744,9 @@
           <t>0</t>
         </is>
       </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -771,6 +794,9 @@
           <t>-0.01</t>
         </is>
       </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -818,6 +844,9 @@
           <t>0.02</t>
         </is>
       </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -865,6 +894,9 @@
           <t>0</t>
         </is>
       </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -912,6 +944,9 @@
           <t>-0.01</t>
         </is>
       </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -959,6 +994,9 @@
           <t>0.02</t>
         </is>
       </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1006,6 +1044,9 @@
           <t>0</t>
         </is>
       </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1053,6 +1094,9 @@
           <t>-0.01</t>
         </is>
       </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1099,6 +1143,9 @@
         <is>
           <t>0.02</t>
         </is>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Gravedigger2026/Assets/ConfigTables/Excel/战斗_技能配置表_Combat_SkillConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Excel/战斗_技能配置表_Combat_SkillConfig.xlsx
@@ -454,7 +454,7 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>技能图标</t>
+          <t>IconAssetId</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
@@ -474,7 +474,7 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>效果已实现</t>
+          <t>EffectImplemented</t>
         </is>
       </c>
     </row>
@@ -516,7 +516,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>UI 图标资源 Id；缺/空=无图</t>
+          <t>（待补 SPEC 中文说明）IconAssetId</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -536,7 +536,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Demo 战斗效果是否已接线；不驱动战斗；UI-021 绿/红</t>
+          <t>（待补 SPEC 中文说明）EffectImplemented</t>
         </is>
       </c>
     </row>
@@ -623,6 +623,7 @@
           <t>CurrentNormalAttackTarget</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>技能01</t>
@@ -633,6 +634,7 @@
           <t>技能01展示描述</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>SkillEffect_01</t>
@@ -648,8 +650,10 @@
           <t>0.02</t>
         </is>
       </c>
-      <c r="L4" t="n">
-        <v>0</v>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -658,8 +662,10 @@
           <t>Skill_01</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>2</v>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -671,6 +677,7 @@
           <t>CurrentNormalAttackTarget</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>技能01</t>
@@ -681,6 +688,7 @@
           <t>技能01展示描述</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>SkillEffect_01</t>
@@ -691,11 +699,15 @@
           <t>5</t>
         </is>
       </c>
-      <c r="K5" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -719,6 +731,7 @@
           <t>CurrentNormalAttackTarget</t>
         </is>
       </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>技能02</t>
@@ -729,6 +742,7 @@
           <t>技能02展示描述</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>SkillEffect_02</t>
@@ -744,8 +758,10 @@
           <t>0</t>
         </is>
       </c>
-      <c r="L6" t="n">
-        <v>0</v>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -769,6 +785,7 @@
           <t>CurrentNormalAttackTarget</t>
         </is>
       </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>技能03</t>
@@ -779,6 +796,7 @@
           <t>技能03展示描述</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>SkillEffect_03</t>
@@ -794,8 +812,10 @@
           <t>-0.01</t>
         </is>
       </c>
-      <c r="L7" t="n">
-        <v>0</v>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -819,6 +839,7 @@
           <t>CurrentNormalAttackTarget</t>
         </is>
       </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>技能04</t>
@@ -829,6 +850,7 @@
           <t>技能04展示描述</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>SkillEffect_04</t>
@@ -844,8 +866,10 @@
           <t>0.02</t>
         </is>
       </c>
-      <c r="L8" t="n">
-        <v>0</v>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -869,6 +893,7 @@
           <t>EnemySingle</t>
         </is>
       </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>技能05</t>
@@ -879,6 +904,7 @@
           <t>技能05展示描述</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>SkillEffect_05</t>
@@ -894,8 +920,10 @@
           <t>0</t>
         </is>
       </c>
-      <c r="L9" t="n">
-        <v>0</v>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -919,6 +947,7 @@
           <t>Self</t>
         </is>
       </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>技能06</t>
@@ -929,6 +958,7 @@
           <t>技能06展示描述</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>SkillEffect_06</t>
@@ -944,8 +974,10 @@
           <t>-0.01</t>
         </is>
       </c>
-      <c r="L10" t="n">
-        <v>0</v>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -969,6 +1001,7 @@
           <t>CurrentNormalAttackTarget</t>
         </is>
       </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>技能07</t>
@@ -979,6 +1012,7 @@
           <t>技能07展示描述</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>SkillEffect_07</t>
@@ -994,8 +1028,10 @@
           <t>0.02</t>
         </is>
       </c>
-      <c r="L11" t="n">
-        <v>0</v>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -1019,6 +1055,7 @@
           <t>AllySingle</t>
         </is>
       </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>技能08</t>
@@ -1029,6 +1066,7 @@
           <t>技能08展示描述</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>SkillEffect_08</t>
@@ -1044,8 +1082,10 @@
           <t>0</t>
         </is>
       </c>
-      <c r="L12" t="n">
-        <v>0</v>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -1069,6 +1109,7 @@
           <t>GroundPoint</t>
         </is>
       </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>技能09</t>
@@ -1079,6 +1120,7 @@
           <t>技能09展示描述</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>SkillEffect_09</t>
@@ -1094,8 +1136,10 @@
           <t>-0.01</t>
         </is>
       </c>
-      <c r="L13" t="n">
-        <v>0</v>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -1119,6 +1163,7 @@
           <t>EnemyAll</t>
         </is>
       </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>技能10</t>
@@ -1129,6 +1174,7 @@
           <t>技能10展示描述</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>SkillEffect_10</t>
@@ -1144,8 +1190,10 @@
           <t>0.02</t>
         </is>
       </c>
-      <c r="L14" t="n">
-        <v>0</v>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/Gravedigger2026/Assets/ConfigTables/Excel/战斗_技能配置表_Combat_SkillConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Excel/战斗_技能配置表_Combat_SkillConfig.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,50 +429,55 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>阵型ID</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>技能CD模式</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>技能释放目标</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>额外激活条件</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>技能名称</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>技能展示描述</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>IconAssetId</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>技能效果ID</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>基础冷却</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>失控概率加成</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>EffectImplemented</t>
         </is>
@@ -491,50 +496,55 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>可选；空=普通士兵技能；非空=阵型标记技能 FK→TacticalFormationConfig</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>Mode1=开战起算CD；Mode2=开战CD=0，释放后再进CD</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Self|AllySingle|AllyAll|EnemySingle|EnemyAll|GroundPoint|CurrentNormalAttackTarget</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>默认空；编码后续专题</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>展示文字或本地化 Key</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>展示文字或本地化 Key</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>（待补 SPEC 中文说明）IconAssetId</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>FK → SkillEffectConfig.SkillEffectId</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>≥0 秒；实际 CD 见 §3.12 公式</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>可正可负；缺省 0；按等级查行后求和</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>（待补 SPEC 中文说明）EffectImplemented</t>
         </is>
@@ -553,50 +563,55 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>FormationId</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>CooldownMode</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>CastTarget</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>ExtraActivationCondition</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>DisplayName</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>IconAssetId</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>SkillEffectId</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>BaseCooldownSeconds</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>LossOfControlChanceBonus</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>EffectImplemented</t>
         </is>
@@ -613,44 +628,42 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Mode1</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>CurrentNormalAttackTarget</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>技能01</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>技能01展示描述</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>SkillEffect_01</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>0.02</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -667,44 +680,42 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Mode1</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>CurrentNormalAttackTarget</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>技能01</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>技能01展示描述</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>SkillEffect_01</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>0.03</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -721,44 +732,42 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Mode1</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>CurrentNormalAttackTarget</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>技能02</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>技能02展示描述</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>SkillEffect_02</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="L6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -775,44 +784,42 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Mode2</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>CurrentNormalAttackTarget</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>技能03</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>技能03展示描述</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>SkillEffect_03</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>-0.01</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -829,44 +836,42 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Mode1</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>CurrentNormalAttackTarget</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>技能04</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>技能04展示描述</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>SkillEffect_04</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>0.02</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -883,44 +888,42 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Mode1</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>EnemySingle</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>技能05</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>技能05展示描述</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>SkillEffect_05</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="L9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -937,44 +940,42 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>Mode2</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>Self</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>技能06</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>技能06展示描述</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>SkillEffect_06</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>-0.01</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -991,44 +992,42 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>Mode1</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>CurrentNormalAttackTarget</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>技能07</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>技能07展示描述</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>SkillEffect_07</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>0.02</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1045,44 +1044,42 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>Mode1</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>AllySingle</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>技能08</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>技能08展示描述</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>SkillEffect_08</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="L12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1099,44 +1096,42 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>Mode2</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>GroundPoint</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>技能09</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>技能09展示描述</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>SkillEffect_09</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>-0.01</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1153,47 +1148,145 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>Mode1</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>EnemyAll</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>技能10</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>技能10展示描述</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>SkillEffect_10</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>0.02</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Skill_Form_Wedge</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Form_Wedge_01</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Mode2</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>楔阵</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>战术阵型标记技能；制造授予后用于组阵判定，不驱动战斗</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Skill_Form_Wedge</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Skill_Form_Wedge_02</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Form_Wedge_02</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Mode2</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>平行阵</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>战术阵型标记技能；制造授予后用于组阵判定，不驱动战斗</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Skill_Form_Wedge_02</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
